--- a/data/data_of_questionaries/questions.xlsx
+++ b/data/data_of_questionaries/questions.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>subquestion</t>
+          <t>subquestion phrase</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>subquestion</t>
+          <t>subquestion phrase</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>subquestion</t>
+          <t>subquestion phrase</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>subquestion</t>
+          <t>subquestion phrase</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>subquestion</t>
+          <t>subquestion phrase</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>subquestion</t>
+          <t>subquestion phrase</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>subquestion</t>
+          <t>subquestion phrase</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>subquestion</t>
+          <t>subquestion phrase</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>subquestion</t>
+          <t>subquestion phrase</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
